--- a/BOM/BOM.XLSX
+++ b/BOM/BOM.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\micro generator\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C11C481-1122-4484-912E-20D92DAD0B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8B1DCE-1DFC-4E2D-8719-7EA188AEA442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3615" yWindow="3405" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>元件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,11 +50,165 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ESP32-WROOM-32E</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MCU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESP32-WROOM-32E*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CH340C*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB to TTL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP1584EN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC-DC BUCK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>usb4105-gf-a</t>
+  </si>
+  <si>
+    <t>TYPE-C母座</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PJ-035D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC輸入接頭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>210K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40.2K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.1K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10uF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22uF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150pF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1uF</t>
+  </si>
+  <si>
+    <t>0.1uF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15uH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12*12mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SS14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B340</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -62,7 +216,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="0000"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +232,13 @@
       <name val="新細明體"/>
       <family val="3"/>
       <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -98,8 +262,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -380,17 +554,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="4" width="9.140625" style="2"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -398,16 +575,218 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="3">
+        <v>603</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="3">
+        <v>603</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="3">
+        <v>603</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="3">
+        <v>603</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="3">
+        <v>603</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="3">
+        <v>603</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="3">
+        <v>603</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="4">
+        <v>805</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="3">
+        <v>603</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="3">
+        <v>603</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="3">
+        <v>603</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="3">
+        <v>603</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/BOM/BOM.XLSX
+++ b/BOM/BOM.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\micro generator\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8B1DCE-1DFC-4E2D-8719-7EA188AEA442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FF68B4-2D91-4785-B333-E66EB184464D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>元件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -38,10 +38,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>價格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>INA228*1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -208,7 +204,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>D3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -564,229 +560,229 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="3">
         <v>603</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3">
         <v>603</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3">
         <v>603</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>603</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="3">
         <v>603</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" s="3">
         <v>603</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="3">
         <v>603</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="4">
         <v>805</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="3">
         <v>603</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="3">
         <v>603</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" s="3">
         <v>603</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="3">
         <v>603</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
